--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2023_araucania.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2023_araucania.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>27.05787105513086</v>
+      </c>
+      <c r="C2">
         <v>30.24127211488061</v>
-      </c>
-      <c r="C2">
-        <v>27.05787105513086</v>
       </c>
       <c r="D2">
         <v>3.30673920131798</v>
       </c>
       <c r="E2">
-        <v>19.22532539302859</v>
+        <v>17.20153747174978</v>
       </c>
       <c r="F2">
         <v>63.57313713522164</v>
       </c>
       <c r="G2">
-        <v>17.20153747174978</v>
+        <v>19.22532539302859</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>29.13669064748202</v>
+      </c>
+      <c r="C3">
         <v>39.52493177871496</v>
-      </c>
-      <c r="C3">
-        <v>29.13669064748202</v>
       </c>
       <c r="D3">
         <v>2.530048642711439</v>
       </c>
       <c r="E3">
+        <v>17.27523441809156</v>
+      </c>
+      <c r="F3">
+        <v>59.29031071888215</v>
+      </c>
+      <c r="G3">
         <v>23.43445486302629</v>
-      </c>
-      <c r="F3">
-        <v>59.29031071888214</v>
-      </c>
-      <c r="G3">
-        <v>17.27523441809156</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>30.33754920847642</v>
+      </c>
+      <c r="C4">
         <v>46.2852835245833</v>
-      </c>
-      <c r="C4">
-        <v>30.33754920847642</v>
       </c>
       <c r="D4">
         <v>2.160513934129569</v>
       </c>
       <c r="E4">
-        <v>26.20571916346564</v>
+        <v>17.17645942998056</v>
       </c>
       <c r="F4">
         <v>56.6178214065538</v>
       </c>
       <c r="G4">
-        <v>17.17645942998056</v>
+        <v>26.20571916346564</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>32.8234658988663</v>
+      </c>
+      <c r="C5">
         <v>34.53302141443225</v>
-      </c>
-      <c r="C5">
-        <v>32.8234658988663</v>
       </c>
       <c r="D5">
         <v>2.895779051589369</v>
       </c>
       <c r="E5">
-        <v>20.63440860215054</v>
+        <v>19.61290322580645</v>
       </c>
       <c r="F5">
         <v>59.75268817204301</v>
       </c>
       <c r="G5">
-        <v>19.61290322580645</v>
+        <v>20.63440860215054</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>26.10619469026549</v>
+      </c>
+      <c r="C6">
         <v>39.66754364984453</v>
-      </c>
-      <c r="C6">
-        <v>26.10619469026549</v>
       </c>
       <c r="D6">
         <v>2.52095266807356</v>
       </c>
       <c r="E6">
-        <v>23.92872601356226</v>
+        <v>15.74808829894676</v>
       </c>
       <c r="F6">
         <v>60.32318568749098</v>
       </c>
       <c r="G6">
-        <v>15.74808829894676</v>
+        <v>23.92872601356226</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>27.95733678086619</v>
+      </c>
+      <c r="C7">
         <v>34.20599008834303</v>
-      </c>
-      <c r="C7">
-        <v>27.95733678086619</v>
       </c>
       <c r="D7">
         <v>2.923464566929134</v>
       </c>
       <c r="E7">
-        <v>21.09354238639384</v>
+        <v>17.24023385596598</v>
       </c>
       <c r="F7">
         <v>61.66622375764018</v>
       </c>
       <c r="G7">
-        <v>17.24023385596599</v>
+        <v>21.09354238639383</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>29.64576407199358</v>
+      </c>
+      <c r="C8">
         <v>46.70411555657457</v>
-      </c>
-      <c r="C8">
-        <v>29.64576407199358</v>
       </c>
       <c r="D8">
         <v>2.141138929798724</v>
       </c>
       <c r="E8">
-        <v>26.48378079698368</v>
+        <v>16.81076513033869</v>
       </c>
       <c r="F8">
         <v>56.70545407267763</v>
       </c>
       <c r="G8">
-        <v>16.81076513033869</v>
+        <v>26.48378079698368</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>31.02894477497536</v>
+      </c>
+      <c r="C9">
         <v>31.58740008030076</v>
-      </c>
-      <c r="C9">
-        <v>31.02894477497536</v>
       </c>
       <c r="D9">
         <v>3.165819274324012</v>
       </c>
       <c r="E9">
-        <v>19.42449272759921</v>
+        <v>19.08107380140061</v>
       </c>
       <c r="F9">
         <v>61.49443347100017</v>
       </c>
       <c r="G9">
-        <v>19.08107380140061</v>
+        <v>19.42449272759921</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>28.77197341449779</v>
+      </c>
+      <c r="C10">
         <v>40.20125473631902</v>
-      </c>
-      <c r="C10">
-        <v>28.77197341449779</v>
       </c>
       <c r="D10">
         <v>2.487484548825711</v>
       </c>
       <c r="E10">
-        <v>23.79149358526633</v>
+        <v>17.02753372789766</v>
       </c>
       <c r="F10">
         <v>59.18097268683602</v>
       </c>
       <c r="G10">
-        <v>17.02753372789766</v>
+        <v>23.79149358526633</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>31.06972518737224</v>
+      </c>
+      <c r="C11">
         <v>45.76425164660458</v>
-      </c>
-      <c r="C11">
-        <v>31.06972518737224</v>
       </c>
       <c r="D11">
         <v>2.185111662531017</v>
       </c>
       <c r="E11">
-        <v>25.87978422810173</v>
+        <v>17.56999743128693</v>
       </c>
       <c r="F11">
         <v>56.55021834061137</v>
       </c>
       <c r="G11">
-        <v>17.56999743128693</v>
+        <v>25.87978422810173</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>30.1460883811951</v>
+      </c>
+      <c r="C12">
         <v>38.99330997132845</v>
-      </c>
-      <c r="C12">
-        <v>30.1460883811951</v>
       </c>
       <c r="D12">
         <v>2.564542483660131</v>
       </c>
       <c r="E12">
-        <v>23.05394860756088</v>
+        <v>17.82322077223194</v>
       </c>
       <c r="F12">
         <v>59.12283062020718</v>
       </c>
       <c r="G12">
-        <v>17.82322077223194</v>
+        <v>23.05394860756088</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>31.00607279619387</v>
+      </c>
+      <c r="C13">
         <v>29.33121881406413</v>
-      </c>
-      <c r="C13">
-        <v>31.00607279619387</v>
       </c>
       <c r="D13">
         <v>3.409336674139523</v>
       </c>
       <c r="E13">
-        <v>18.29344784328862</v>
+        <v>19.33802952812892</v>
       </c>
       <c r="F13">
         <v>62.36852262858245</v>
       </c>
       <c r="G13">
-        <v>19.33802952812892</v>
+        <v>18.29344784328862</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>30.22203947368421</v>
+      </c>
+      <c r="C14">
         <v>36.06085526315789</v>
-      </c>
-      <c r="C14">
-        <v>30.22203947368421</v>
       </c>
       <c r="D14">
         <v>2.77309007981756</v>
       </c>
       <c r="E14">
-        <v>21.6864490603363</v>
+        <v>18.17507418397626</v>
       </c>
       <c r="F14">
         <v>60.13847675568744</v>
       </c>
       <c r="G14">
-        <v>18.17507418397626</v>
+        <v>21.6864490603363</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>28.60646854144088</v>
+      </c>
+      <c r="C15">
         <v>39.17631623980377</v>
-      </c>
-      <c r="C15">
-        <v>28.60646854144088</v>
       </c>
       <c r="D15">
         <v>2.552562609202097</v>
       </c>
       <c r="E15">
-        <v>23.34942544366628</v>
+        <v>17.04970422247909</v>
       </c>
       <c r="F15">
         <v>59.60087033385462</v>
       </c>
       <c r="G15">
-        <v>17.04970422247909</v>
+        <v>23.34942544366628</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>28.91705544775195</v>
+      </c>
+      <c r="C16">
         <v>28.48767598365055</v>
-      </c>
-      <c r="C16">
-        <v>28.91705544775195</v>
       </c>
       <c r="D16">
         <v>3.510289855072464</v>
       </c>
       <c r="E16">
-        <v>18.09836065573771</v>
+        <v>18.37114754098361</v>
       </c>
       <c r="F16">
         <v>63.53049180327869</v>
       </c>
       <c r="G16">
-        <v>18.37114754098361</v>
+        <v>18.09836065573771</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>32.71940667490729</v>
+      </c>
+      <c r="C17">
         <v>43.31273176761434</v>
-      </c>
-      <c r="C17">
-        <v>32.71940667490729</v>
       </c>
       <c r="D17">
         <v>2.308789954337899</v>
       </c>
       <c r="E17">
+        <v>18.58717786672284</v>
+      </c>
+      <c r="F17">
+        <v>56.8078084404185</v>
+      </c>
+      <c r="G17">
         <v>24.60501369285865</v>
-      </c>
-      <c r="F17">
-        <v>56.80780844041852</v>
-      </c>
-      <c r="G17">
-        <v>18.58717786672284</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>29.13448207565855</v>
+      </c>
+      <c r="C18">
         <v>44.07803525450584</v>
-      </c>
-      <c r="C18">
-        <v>29.13448207565855</v>
       </c>
       <c r="D18">
         <v>2.268703662098405</v>
       </c>
       <c r="E18">
-        <v>25.4473729346521</v>
+        <v>16.82007889771883</v>
       </c>
       <c r="F18">
         <v>57.73254816762907</v>
       </c>
       <c r="G18">
-        <v>16.82007889771883</v>
+        <v>25.4473729346521</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>28.30508474576271</v>
+      </c>
+      <c r="C19">
         <v>42.44992295839754</v>
-      </c>
-      <c r="C19">
-        <v>28.30508474576271</v>
       </c>
       <c r="D19">
         <v>2.355716878402904</v>
       </c>
       <c r="E19">
-        <v>24.86013354990074</v>
+        <v>16.57643024724779</v>
       </c>
       <c r="F19">
         <v>58.56343620285147</v>
       </c>
       <c r="G19">
-        <v>16.57643024724779</v>
+        <v>24.86013354990074</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>28.78201240845267</v>
+      </c>
+      <c r="C20">
         <v>30.72258245090265</v>
-      </c>
-      <c r="C20">
-        <v>28.78201240845267</v>
       </c>
       <c r="D20">
         <v>3.25493470999089</v>
       </c>
       <c r="E20">
-        <v>19.26125230310297</v>
+        <v>18.04462901763519</v>
       </c>
       <c r="F20">
-        <v>62.69411867926183</v>
+        <v>62.69411867926184</v>
       </c>
       <c r="G20">
-        <v>18.04462901763518</v>
+        <v>19.26125230310298</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>31.16888744448055</v>
+      </c>
+      <c r="C21">
         <v>32.85234535803271</v>
-      </c>
-      <c r="C21">
-        <v>31.16888744448055</v>
       </c>
       <c r="D21">
         <v>3.043922706588406</v>
       </c>
       <c r="E21">
-        <v>20.02932473845503</v>
+        <v>19.00295889252879</v>
       </c>
       <c r="F21">
         <v>60.96771636901617</v>
       </c>
       <c r="G21">
-        <v>19.00295889252879</v>
+        <v>20.02932473845503</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>33.9924670433145</v>
+      </c>
+      <c r="C22">
         <v>34.16902071563089</v>
-      </c>
-      <c r="C22">
-        <v>33.9924670433145</v>
       </c>
       <c r="D22">
         <v>2.926627626593179</v>
       </c>
       <c r="E22">
-        <v>20.31917127458529</v>
+        <v>20.21418072373486</v>
       </c>
       <c r="F22">
         <v>59.46664800167985</v>
       </c>
       <c r="G22">
-        <v>20.21418072373486</v>
+        <v>20.31917127458529</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>28.85380996130182</v>
+      </c>
+      <c r="C23">
         <v>35.43806898855759</v>
-      </c>
-      <c r="C23">
-        <v>28.85380996130182</v>
       </c>
       <c r="D23">
         <v>2.821824181004007</v>
       </c>
       <c r="E23">
-        <v>21.5701891140785</v>
+        <v>17.56252965498543</v>
       </c>
       <c r="F23">
         <v>60.86728123093609</v>
       </c>
       <c r="G23">
-        <v>17.56252965498543</v>
+        <v>21.5701891140785</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>29.47588126159555</v>
+      </c>
+      <c r="C24">
         <v>34.03293135435992</v>
-      </c>
-      <c r="C24">
-        <v>29.47588126159555</v>
       </c>
       <c r="D24">
         <v>2.938330494037479</v>
       </c>
       <c r="E24">
-        <v>20.81412665768385</v>
+        <v>18.0270902772853</v>
       </c>
       <c r="F24">
         <v>61.15878306503084</v>
       </c>
       <c r="G24">
-        <v>18.0270902772853</v>
+        <v>20.81412665768385</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>29.0653115628124</v>
+      </c>
+      <c r="C25">
         <v>45.01832722425858</v>
-      </c>
-      <c r="C25">
-        <v>29.0653115628124</v>
       </c>
       <c r="D25">
         <v>2.221317542561066</v>
       </c>
       <c r="E25">
-        <v>25.86017131645691</v>
+        <v>16.69617648466287</v>
       </c>
       <c r="F25">
         <v>57.44365219888022</v>
       </c>
       <c r="G25">
-        <v>16.69617648466287</v>
+        <v>25.86017131645691</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>37.85622357050929</v>
+      </c>
+      <c r="C26">
         <v>33.05754734326163</v>
-      </c>
-      <c r="C26">
-        <v>37.85622357050929</v>
       </c>
       <c r="D26">
         <v>3.025027808676307</v>
       </c>
       <c r="E26">
-        <v>19.34165232358004</v>
+        <v>22.14931153184165</v>
       </c>
       <c r="F26">
         <v>58.50903614457831</v>
       </c>
       <c r="G26">
-        <v>22.14931153184165</v>
+        <v>19.34165232358004</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>32.88755458515284</v>
+      </c>
+      <c r="C27">
         <v>34.67521834061135</v>
-      </c>
-      <c r="C27">
-        <v>32.88755458515284</v>
       </c>
       <c r="D27">
         <v>2.883903974813066</v>
       </c>
       <c r="E27">
-        <v>20.69386757879306</v>
+        <v>19.6270054564704</v>
       </c>
       <c r="F27">
         <v>59.67912696473654</v>
       </c>
       <c r="G27">
-        <v>19.6270054564704</v>
+        <v>20.69386757879306</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>29.52029520295203</v>
+      </c>
+      <c r="C28">
         <v>40.72064250054265</v>
-      </c>
-      <c r="C28">
-        <v>29.52029520295203</v>
       </c>
       <c r="D28">
         <v>2.455756929637527</v>
       </c>
       <c r="E28">
+        <v>17.34030345531047</v>
+      </c>
+      <c r="F28">
+        <v>58.74027795486422</v>
+      </c>
+      <c r="G28">
         <v>23.91941858982532</v>
-      </c>
-      <c r="F28">
-        <v>58.7402779548642</v>
-      </c>
-      <c r="G28">
-        <v>17.34030345531047</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>29.57406449387825</v>
+      </c>
+      <c r="C29">
         <v>38.5583721331264</v>
-      </c>
-      <c r="C29">
-        <v>29.57406449387825</v>
       </c>
       <c r="D29">
         <v>2.593470483005367</v>
       </c>
       <c r="E29">
-        <v>22.93333333333333</v>
+        <v>17.58974358974359</v>
       </c>
       <c r="F29">
         <v>59.47692307692307</v>
       </c>
       <c r="G29">
-        <v>17.58974358974359</v>
+        <v>22.93333333333333</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>29.47914154810706</v>
+      </c>
+      <c r="C30">
         <v>39.36580660718592</v>
-      </c>
-      <c r="C30">
-        <v>29.47914154810706</v>
       </c>
       <c r="D30">
         <v>2.540275650842267</v>
       </c>
       <c r="E30">
-        <v>23.31476720936875</v>
+        <v>17.45929734361611</v>
       </c>
       <c r="F30">
         <v>59.22593544701515</v>
       </c>
       <c r="G30">
-        <v>17.45929734361611</v>
+        <v>23.31476720936875</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>28.15997987674506</v>
+      </c>
+      <c r="C31">
         <v>32.42359451641303</v>
-      </c>
-      <c r="C31">
-        <v>28.15997987674506</v>
       </c>
       <c r="D31">
         <v>3.084173778122576</v>
       </c>
       <c r="E31">
-        <v>20.19110275689223</v>
+        <v>17.5360275689223</v>
       </c>
       <c r="F31">
         <v>62.27286967418546</v>
       </c>
       <c r="G31">
-        <v>17.5360275689223</v>
+        <v>20.19110275689223</v>
       </c>
     </row>
     <row r="32">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="B32">
+        <v>31.33427082471669</v>
+      </c>
+      <c r="C32">
         <v>43.68434113657044</v>
-      </c>
-      <c r="C32">
-        <v>31.33427082471669</v>
       </c>
       <c r="D32">
         <v>2.289149782238213</v>
       </c>
       <c r="E32">
+        <v>17.90339351545515</v>
+      </c>
+      <c r="F32">
+        <v>57.13678041402778</v>
+      </c>
+      <c r="G32">
         <v>24.95982607051706</v>
-      </c>
-      <c r="F32">
-        <v>57.13678041402779</v>
-      </c>
-      <c r="G32">
-        <v>17.90339351545515</v>
       </c>
     </row>
     <row r="33">
@@ -1173,22 +1173,22 @@
         </is>
       </c>
       <c r="B33">
+        <v>29.11217247690042</v>
+      </c>
+      <c r="C33">
         <v>39.6375485426059</v>
-      </c>
-      <c r="C33">
-        <v>29.11217247690042</v>
       </c>
       <c r="D33">
         <v>2.52286036036036</v>
       </c>
       <c r="E33">
-        <v>23.48895648723714</v>
+        <v>17.25168628488295</v>
       </c>
       <c r="F33">
         <v>59.25935722787992</v>
       </c>
       <c r="G33">
-        <v>17.25168628488295</v>
+        <v>23.48895648723714</v>
       </c>
     </row>
   </sheetData>
